--- a/results/Int Task Remove ACC -0.2/Rando_fi_explain.xlsx
+++ b/results/Int Task Remove ACC -0.2/Rando_fi_explain.xlsx
@@ -1148,268 +1148,268 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.892994633754812e-05</v>
+        <v>0.001571822432359745</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0002182514402208268</v>
+        <v>0.002192738667836412</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0008109933698089977</v>
+        <v>0.003008956051075732</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.001326154712942711</v>
+        <v>0.000404481986827695</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.00103265283194838</v>
+        <v>0.00196695971331265</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001962947556235569</v>
+        <v>0.0001689729241797344</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0001312359518720551</v>
+        <v>0.0001256364865087012</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.001040298493984502</v>
+        <v>4.553577847835498e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01138174843004997</v>
+        <v>0.009108833096216096</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00920331907490537</v>
+        <v>0.01308054865211567</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0001897190412644322</v>
+        <v>-0.0006244303794759886</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0005049330260404884</v>
+        <v>0.001805990293932327</v>
       </c>
       <c r="O3" t="n">
-        <v>0.004059225767611104</v>
+        <v>0.004251854483624166</v>
       </c>
       <c r="P3" t="n">
-        <v>0.009034698258240378</v>
+        <v>0.01157834222821387</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.006061430189702113</v>
+        <v>0.004364158612078846</v>
       </c>
       <c r="R3" t="n">
-        <v>0.000980985247104853</v>
+        <v>-0.0006735964148523477</v>
       </c>
       <c r="S3" t="n">
-        <v>0.002154499917047434</v>
+        <v>0.00261812629710723</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.001064938472356499</v>
+        <v>0.0007524245141993901</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001750374853963013</v>
+        <v>0.003909353733894546</v>
       </c>
       <c r="V3" t="n">
-        <v>9.323471668629346e-05</v>
+        <v>-6.630302190630321e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>0.004951030802665228</v>
+        <v>0.00717706817958606</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0005003633902260441</v>
+        <v>-0.001845652081288576</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.613585982429785e-05</v>
+        <v>0.0008204514797192531</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0004351891624583647</v>
+        <v>-0.0005299542295734039</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0001497153942999608</v>
+        <v>0.001002281811669443</v>
       </c>
       <c r="AB3" t="n">
-        <v>-7.967372091291283e-05</v>
+        <v>-7.119706783240918e-05</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.0008973380435826196</v>
+        <v>-0.001090451473555298</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.000220268615484408</v>
+        <v>-0.003119563743842706</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.000513291277538328</v>
+        <v>-0.002762666047517633</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.002236965745042608</v>
+        <v>-0.003992310259554442</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.0005635367016462344</v>
+        <v>0.0001584551442210813</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0.0001984838127057964</v>
+        <v>0.0002268446511808286</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.0006645450827915035</v>
+        <v>-0.002925208460537226</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.001731548235704274</v>
+        <v>-0.001974924868073188</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.0003515749905944565</v>
+        <v>-0.0002957503444426024</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.0001391644792181601</v>
+        <v>-0.0001341133738226241</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0.001989422693267536</v>
+        <v>-0.0003013625712175972</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.0009294933090080115</v>
+        <v>-0.003024906617075934</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.0005990050960861572</v>
+        <v>0.0002337554559983557</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.0002647976601582935</v>
+        <v>0.002938705558243376</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.0001124350812829901</v>
+        <v>-0.0007958638263482973</v>
       </c>
       <c r="AS3" t="n">
-        <v>-0.002625581903664271</v>
+        <v>-0.0009694361865048961</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.003427971314039181</v>
+        <v>-0.008383990397961833</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.002329248779247829</v>
+        <v>0.003584378288463382</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.003975149022382741</v>
+        <v>0.001780920642911722</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.001692053680528643</v>
+        <v>0.0008225492409597568</v>
       </c>
       <c r="AX3" t="n">
-        <v>5.808233818225039e-05</v>
+        <v>6.568956078225275e-05</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.486100897984077e-05</v>
+        <v>0.0008202159703511958</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.005377034981630171</v>
+        <v>-0.001371726459176719</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0.008211908826210776</v>
+        <v>-0.008675129683042761</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0.006364206885982446</v>
+        <v>-0.006412113956087154</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.0001991590016908307</v>
+        <v>-3.019492681670789e-05</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.000361366797817918</v>
+        <v>0.000303936398579977</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.000693477784055363</v>
+        <v>-0.0002268869608501478</v>
       </c>
       <c r="BF3" t="n">
-        <v>-0.008889957696116477</v>
+        <v>-0.006276016776485331</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.002673258387695247</v>
+        <v>-0.001160815916994551</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>3.421142661648168e-06</v>
       </c>
       <c r="BI3" t="n">
-        <v>-5.010782438813701e-05</v>
+        <v>-0.0001756165645418072</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.0007710092040197302</v>
+        <v>0.001603508946715643</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0.005412103153429186</v>
+        <v>-0.003496996951266805</v>
       </c>
       <c r="BL3" t="n">
-        <v>1.801790216165778e-05</v>
+        <v>0.0004845652102643483</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.0004269582088163815</v>
+        <v>0.001307531966073254</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0.004598674233376583</v>
+        <v>-0.007182489695880969</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.001160165704403263</v>
+        <v>0.000501860564251082</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.003077168471144036</v>
+        <v>0.002917844632268303</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.00010088484382624</v>
+        <v>-0.0001795378859003727</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.001916943894765053</v>
+        <v>-0.00103994334128361</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0.001247392322952699</v>
+        <v>-0.000881910948966308</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.0001686564317517259</v>
+        <v>-0.0002167635260743173</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.003422682189825202</v>
+        <v>0.003335460414017258</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.0006413265689417235</v>
+        <v>0.0006282066274615184</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.002050049139120867</v>
+        <v>0.00284072794571045</v>
       </c>
       <c r="BX3" t="n">
-        <v>8.839464230903759e-05</v>
+        <v>-0.0001141808059062388</v>
       </c>
       <c r="BY3" t="n">
-        <v>-2.837636872249583e-05</v>
+        <v>-0.0002573760130545267</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0.0006210931266936603</v>
+        <v>-0.0001137301051398909</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>6.445375443120405e-06</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.0003610940606305978</v>
+        <v>-0.0004054179405674962</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.001727317576140645</v>
+        <v>0.001947041090429762</v>
       </c>
       <c r="CD3" t="n">
-        <v>-9.03398684257073e-05</v>
+        <v>1.582589574423032e-05</v>
       </c>
       <c r="CE3" t="n">
-        <v>-3.308745110924821e-05</v>
+        <v>0.0003942253237091909</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.00155865349166701</v>
+        <v>-0.001365345263157067</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.001907563037470909</v>
+        <v>0.002215399961195458</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.0002901636591826729</v>
+        <v>-0.000125227423595562</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.0009278334549303602</v>
+        <v>-0.00123895791878164</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.001896140725071925</v>
+        <v>-0.001312063043385532</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0.000611304996235501</v>
+        <v>0.000545444382283703</v>
       </c>
     </row>
     <row r="4">
@@ -1419,268 +1419,268 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.005313301133043063</v>
+        <v>0.006549316776769861</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.008773110052254614</v>
+        <v>0.004698075672303535</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004192605673672419</v>
+        <v>0.008453650228969057</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003036236769754613</v>
+        <v>0.005906742745361827</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006981285944014451</v>
+        <v>0.007105431850670049</v>
       </c>
       <c r="H4" t="n">
-        <v>0.006086153319814723</v>
+        <v>0.005030812695770066</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0003889585022483372</v>
+        <v>0.0003059974558452141</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00480090392870365</v>
+        <v>0.004261316120875436</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01969309874731051</v>
+        <v>0.01500230372406759</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02473938552545729</v>
+        <v>0.01868516326985491</v>
       </c>
       <c r="M4" t="n">
-        <v>0.003130563819494625</v>
+        <v>0.005041077319275287</v>
       </c>
       <c r="N4" t="n">
-        <v>0.003345361503126837</v>
+        <v>0.007505126394615591</v>
       </c>
       <c r="O4" t="n">
-        <v>0.006375573612775433</v>
+        <v>0.009984212478404019</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01658888229573438</v>
+        <v>0.01961466539661263</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01016306175451021</v>
+        <v>0.009917873228945887</v>
       </c>
       <c r="R4" t="n">
-        <v>0.003513328056014296</v>
+        <v>0.002341151959892391</v>
       </c>
       <c r="S4" t="n">
-        <v>0.004572660022493597</v>
+        <v>0.005391982746799112</v>
       </c>
       <c r="T4" t="n">
-        <v>0.004326146735683874</v>
+        <v>0.003660649863005137</v>
       </c>
       <c r="U4" t="n">
-        <v>0.005816487521211657</v>
+        <v>0.005677978027127579</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0001739951711738032</v>
+        <v>0.0002991015899527006</v>
       </c>
       <c r="W4" t="n">
-        <v>0.008824824771297252</v>
+        <v>0.008938265181995496</v>
       </c>
       <c r="X4" t="n">
-        <v>0.006368680260250667</v>
+        <v>0.004701392550358742</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.003734978518552762</v>
+        <v>0.002574022853093233</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.002025715956407842</v>
+        <v>0.001822710250207444</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.003659462784566714</v>
+        <v>0.003259895076187446</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0003626328926658376</v>
+        <v>0.001085760423397235</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.006820438686076012</v>
+        <v>0.004523342067217852</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.006342813110588323</v>
+        <v>0.006871277286563201</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.008036840825058515</v>
+        <v>0.004506560984540467</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.005891204649711381</v>
+        <v>0.005594551153478885</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0008544611274134936</v>
+        <v>0.0004446170666723667</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.0007123695761110618</v>
+        <v>0.0006569307100615234</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.005088121368319765</v>
+        <v>0.00493937923693531</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.005000234122888555</v>
+        <v>0.006878691442560957</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.002548332210131583</v>
+        <v>0.001172634792447792</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.001003584638455455</v>
+        <v>0.0009271813511310036</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.003920380682063433</v>
+        <v>0.002735661701238242</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.003747571148872049</v>
+        <v>0.005000491921581746</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.00126670718355386</v>
+        <v>0.001658864713033236</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.002366729813413159</v>
+        <v>0.003562932796554896</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.005649219437431621</v>
+        <v>0.007163404986133448</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.004212046639674043</v>
+        <v>0.003274297824983356</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.00756171382404882</v>
+        <v>0.012299140037748</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.006115638323576705</v>
+        <v>0.008694704594894522</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.003119075569136735</v>
+        <v>0.002854247408280551</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.003938678118132657</v>
+        <v>0.003897721260332655</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0005322052295620899</v>
+        <v>0.0006242061657142541</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.002679963979165473</v>
+        <v>0.00294083174675179</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.00643814663599503</v>
+        <v>0.00806544588611074</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.01014443311813883</v>
+        <v>0.01063276968471701</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.00930333728162055</v>
+        <v>0.009856423393374768</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.001128667180983961</v>
+        <v>0.0007571991942117237</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.0007340911438625552</v>
+        <v>0.0009006499053989577</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.001225627025523082</v>
+        <v>0.0005257179954145591</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.01255101185447164</v>
+        <v>0.01558867816986094</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.007608572887993144</v>
+        <v>0.009438858417144863</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>1.081860301117899e-05</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.000957727114695685</v>
+        <v>0.001264924237410611</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.004300654668470409</v>
+        <v>0.002502386783694212</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.007306320471087164</v>
+        <v>0.00722473183887198</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0009815767661250975</v>
+        <v>0.001229409004814531</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.002337777502899619</v>
+        <v>0.005171478219728653</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.008925236398439203</v>
+        <v>0.00917355154006084</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.004006069617457084</v>
+        <v>0.00397480214688279</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.002589384902837063</v>
+        <v>0.003673040335800554</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.0003480016436419995</v>
+        <v>0.0003658129705561484</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.004862835085398108</v>
+        <v>0.005799528120710348</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.003667245208602692</v>
+        <v>0.005356307848839346</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.001684780881790565</v>
+        <v>0.001724485372730517</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.009553526233150563</v>
+        <v>0.008747974047688126</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.003824769066608451</v>
+        <v>0.004601743905399982</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.005251860085944382</v>
+        <v>0.008870496420984489</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.0002073047849220828</v>
+        <v>0.0004338337399928134</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.0014255701853751</v>
+        <v>0.001413286042446327</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.001426275972448891</v>
+        <v>0.0008683958872266696</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>2.038206677517753e-05</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.001293166728006091</v>
+        <v>0.001519076087506995</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.005472971196503132</v>
+        <v>0.00443673203855104</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.0002871834473529039</v>
+        <v>3.034647689896885e-05</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.0009291183662667986</v>
+        <v>0.0006075242777559161</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.003268244404472696</v>
+        <v>0.002593182247902824</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.004729387587597137</v>
+        <v>0.006118509814214513</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.001022441971308672</v>
+        <v>0.001278849259966026</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.003203134725066641</v>
+        <v>0.003592129786300525</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.004590405242601496</v>
+        <v>0.004755573947870386</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.002751851795784215</v>
+        <v>0.003359582123885447</v>
       </c>
     </row>
     <row r="5">
@@ -1690,268 +1690,268 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.006831056314561812</v>
+        <v>-0.008233387358184796</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.02042652449183607</v>
+        <v>-0.005687660668380445</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.006064645118293899</v>
+        <v>-0.01403565640194491</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.007142857142857184</v>
+        <v>-0.006284241057041529</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.01160453808752029</v>
+        <v>-0.01098865478119936</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.005431522825724744</v>
+        <v>-0.01039653448850381</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0003856041131104826</v>
+        <v>-0.0001285347043701535</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.0104631789403532</v>
+        <v>-0.008263912029323505</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.01817595874959721</v>
+        <v>-0.02007734450531742</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.02619736419157827</v>
+        <v>-0.02120528520786333</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.006677471636953025</v>
+        <v>-0.008001285347043663</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.004764991896272319</v>
+        <v>-0.009789303079416545</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.005251215559157252</v>
+        <v>-0.009854132901134526</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.02379206931022993</v>
+        <v>-0.0211929356881039</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.005914496946319537</v>
+        <v>-0.01018577834721334</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.006364545151616141</v>
+        <v>-0.003798733755414807</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.00566477840719759</v>
+        <v>-0.005348460291734214</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.007527226137091647</v>
+        <v>-0.006943105110896774</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.004598467177607468</v>
+        <v>-0.004755784061696644</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.0001601537475977133</v>
+        <v>-0.0006105398457583288</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.01424581005586592</v>
+        <v>-0.004407200496585928</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.01042985671442853</v>
+        <v>-0.006245996156310074</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.005785920925747345</v>
+        <v>-0.002626521460602216</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.002982171799027578</v>
+        <v>-0.003565640194489483</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.004438237119801347</v>
+        <v>-0.004772581678411292</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.0006997667444185396</v>
+        <v>-0.001427684667908069</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.009868209578913545</v>
+        <v>-0.008904548366431796</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.009543701799485816</v>
+        <v>-0.01320694087403597</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.01205400192864033</v>
+        <v>-0.008904548366431763</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.009578913532626198</v>
+        <v>-0.01034704370179946</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.002032655781406234</v>
+        <v>-0.0004137492043283952</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.001606683804627207</v>
+        <v>-0.0006406149903907865</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.01172325432415121</v>
+        <v>-0.01163239074550124</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.01192935688103965</v>
+        <v>-0.01285347043701797</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.006064645118293899</v>
+        <v>-0.002178090967328639</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.001489757914338907</v>
+        <v>-0.001932689103632057</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.006428801028608178</v>
+        <v>-0.004804612427930832</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.008453873352619745</v>
+        <v>-0.01150385604113107</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.003021536483445852</v>
+        <v>-0.002914798206278035</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.003182256509161063</v>
+        <v>-0.0006842285323298448</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.007682417229186778</v>
+        <v>-0.009643539147040059</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.01348494554772587</v>
+        <v>-0.006886611146700838</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.01726457399103143</v>
+        <v>-0.0407431133888533</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.005188981422165295</v>
+        <v>-0.008655490933971999</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.001066311229590145</v>
+        <v>-0.003318508381799568</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.004596592735454863</v>
+        <v>-0.005637411915438817</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.0007448789571694481</v>
+        <v>-0.0007131280388979255</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.004516335682255001</v>
+        <v>-0.004717566728739875</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.02014734144778989</v>
+        <v>-0.01217168481742472</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.03215887251761694</v>
+        <v>-0.0353619474695708</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.02395900064061503</v>
+        <v>-0.0325752722613709</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.001385755720270776</v>
+        <v>-0.001024983984625272</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.001901385755720319</v>
+        <v>-0.00167579761521105</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.002451893234016123</v>
+        <v>-0.001613904407200439</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.03885329916720053</v>
+        <v>-0.04647661755285074</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.01659684176603294</v>
+        <v>-0.02104420243433696</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.001417982597486334</v>
+        <v>-0.001505445227418323</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.005598133955348206</v>
+        <v>-0.002088688946015404</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.01857783472133251</v>
+        <v>-0.01438180653427291</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.002265911362879069</v>
+        <v>-0.00118894601542413</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.003507138423339507</v>
+        <v>-0.00714285714285714</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.02274183215887253</v>
+        <v>-0.02158872517616911</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.006029173419773148</v>
+        <v>-0.005186385737439281</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.0005765534913517278</v>
+        <v>-0.004676489429852648</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0.0005331556147950778</v>
+        <v>-0.0008552856654123087</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.003998667110963005</v>
+        <v>-0.008563812062645726</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.008744394618834117</v>
+        <v>-0.01012171684817425</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.003865378207264236</v>
+        <v>-0.002928071292170542</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.009996785599485724</v>
+        <v>-0.006085842408712361</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.005531489503498843</v>
+        <v>-0.006426735218508983</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.00570147341447792</v>
+        <v>-0.003600248292985675</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.0002562459961563235</v>
+        <v>-0.0009548058561424932</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.002110490378646779</v>
+        <v>-0.002754644458680344</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.004050144648023157</v>
+        <v>-0.00167579761521105</v>
       </c>
       <c r="CA5" t="n">
         <v>0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0.001832208293153348</v>
+        <v>-0.00324654451944707</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.004823811152925117</v>
+        <v>-0.004892234006158125</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0.0009000321440051807</v>
+        <v>0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.002232589136954388</v>
+        <v>-0.0006047103755569272</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.01016327890703098</v>
+        <v>-0.006090879793747972</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.005998000666444503</v>
+        <v>-0.005637411915438828</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.0007779578606158966</v>
+        <v>-0.002049967969250499</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.004898367210929688</v>
+        <v>-0.008552856654122531</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0.002577975811584976</v>
+        <v>-0.008847867600254578</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.00589951377633714</v>
+        <v>-0.004376012965964371</v>
       </c>
     </row>
     <row r="6">
@@ -1961,268 +1961,268 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.00360216311814108</v>
+        <v>-0.001181738529221773</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.00198289912740168</v>
+        <v>-0.001293471938590238</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.001253155521733349</v>
+        <v>0.001797183295503341</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.003064567250107286</v>
+        <v>-0.002932607792341219</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.003463799759376723</v>
+        <v>-0.001216881450257615</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.001083800781844444</v>
+        <v>-0.001533405943287425</v>
       </c>
       <c r="I6" t="n">
-        <v>-5.6348003203327e-05</v>
+        <v>-3.206471932510336e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.001529660370227734</v>
+        <v>-0.002505268811272182</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.005755096587323483</v>
+        <v>0.002461847664423986</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.01044291847017922</v>
+        <v>-0.0008100734319668847</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0002291269622100273</v>
+        <v>-0.002566137685905365</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.001889491352551525</v>
+        <v>-0.002785415017917736</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0009873300243012667</v>
+        <v>-6.603671032919808e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0009643721038615161</v>
+        <v>0.002351688672234345</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.973612041766934e-05</v>
+        <v>-0.003527128796060069</v>
       </c>
       <c r="R6" t="n">
-        <v>2.627322901288255e-05</v>
+        <v>-0.00224532405766317</v>
       </c>
       <c r="S6" t="n">
-        <v>0.000302607076350131</v>
+        <v>-0.001945734228767068</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.004506158120088472</v>
+        <v>-0.0007447149263292707</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.001730752605067232</v>
+        <v>0.000665362672422376</v>
       </c>
       <c r="V6" t="n">
-        <v>7.759155803824247e-06</v>
+        <v>-0.0002181447738646203</v>
       </c>
       <c r="W6" t="n">
-        <v>0.00329094459497396</v>
+        <v>-0.0007012270600951526</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.004758573371825123</v>
+        <v>-0.005036563118542589</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.002849375434411861</v>
+        <v>-0.0003939205802094086</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.001209130970573449</v>
+        <v>-0.001786820746374096</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.002671925177830381</v>
+        <v>-0.001378536699011756</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.0001637650615386593</v>
+        <v>-0.0007415853131713529</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.004168991534952995</v>
+        <v>-0.004018428842418062</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.003626473829783031</v>
+        <v>-0.007623318385650246</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.004297808138803936</v>
+        <v>-0.005769857829583253</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.006948460952226629</v>
+        <v>-0.007387628285159498</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.001243400471584033</v>
+        <v>-0.0001843054679536133</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.0003753926087827319</v>
+        <v>-0.0003909081436531125</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.003600513144432774</v>
+        <v>-0.003931774503523391</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.00325963739807619</v>
+        <v>-0.003869517052686719</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.0007266150596537569</v>
+        <v>-0.0009747656016171253</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.0009474553623552096</v>
+        <v>-0.0008281120370991018</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.005087474979889797</v>
+        <v>-0.002074670514093682</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.002651728178331422</v>
+        <v>-0.006777854860241499</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.00142995256118986</v>
+        <v>-0.000907821229050243</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.00181238536464475</v>
+        <v>0.0006347872917973618</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.003833478206389027</v>
+        <v>-0.005997876213092576</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.003252809140695126</v>
+        <v>-0.002688838520716364</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.007169966420737244</v>
+        <v>-0.009181844590791882</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.002335171721133814</v>
+        <v>0.0001325408534818828</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.001588038908190479</v>
+        <v>-0.0001661706865877937</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.0001052671965187269</v>
+        <v>-0.0001284458671794497</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.0003770070450571761</v>
+        <v>-0.000568183628080357</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.0007763888724646368</v>
+        <v>-0.0008663538747592486</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.006488782280873575</v>
+        <v>-0.008452937529478182</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.01226172149121095</v>
+        <v>-0.01190811058658459</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.01280483844452026</v>
+        <v>-0.006216338366156926</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.0002953941291997553</v>
+        <v>-0.0006692461727811154</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.0005911937880175161</v>
+        <v>-8.715002913306513e-05</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.001897446591492136</v>
+        <v>-0.0003215271336458464</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.009256817234315037</v>
+        <v>-0.00872641735242442</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.00489599063944576</v>
+        <v>-0.006343114548395349</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0.000650475356084751</v>
+        <v>-0.001141258107462117</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-0.002569096142898966</v>
+        <v>0.0003540166303737241</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.01035864501141063</v>
+        <v>-0.008702820708524723</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0.0003777023894812353</v>
+        <v>-0.0004928572681307502</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.002328434833678328</v>
+        <v>-0.0005292382372936472</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.005209505251158419</v>
+        <v>-0.01416753066384755</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.001410964656026476</v>
+        <v>-0.001803884045899063</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.001403131261301943</v>
+        <v>0.002345131956871305</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-3.063457949889214e-05</v>
+        <v>-0.0004306219236480391</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0.002629748643542182</v>
+        <v>-0.005661847539994683</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.003495031294690309</v>
+        <v>-0.002865299188671313</v>
       </c>
       <c r="BT6" t="n">
-        <v>-8.076720071111264e-05</v>
+        <v>-0.001237520905298498</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0.003717503446858364</v>
+        <v>-0.005153400902030363</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.0004659125716986262</v>
+        <v>-0.001939723559044676</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.0006682311878064035</v>
+        <v>-0.002058489126711452</v>
       </c>
       <c r="BX6" t="n">
-        <v>-7.788912153854909e-05</v>
+        <v>-0.0002806613136880909</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.001053130528797405</v>
+        <v>-0.0009624876983976959</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.001114819588843144</v>
+        <v>-0.0005527620140012984</v>
       </c>
       <c r="CA6" t="n">
         <v>0</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0.0003158550759157636</v>
+        <v>-0.001202035681614955</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0.002464326436588973</v>
+        <v>-0.000680713128038915</v>
       </c>
       <c r="CD6" t="n">
-        <v>-2.431118314425163e-05</v>
+        <v>0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.0002279503055599985</v>
+        <v>-3.969521343131499e-05</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.001701332983861931</v>
+        <v>-0.002159780329990809</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.0003776736206603821</v>
+        <v>-0.003643799084875673</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.0003976229085498995</v>
+        <v>-0.0006094675246312437</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.001318739976992278</v>
+        <v>-0.00173913295616562</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0.0008717244782016852</v>
+        <v>-0.004906126742719308</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0.002682935515266896</v>
+        <v>-0.0009643643316594147</v>
       </c>
     </row>
     <row r="7">
@@ -2232,268 +2232,268 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.0006662163997519122</v>
+        <v>0.001185137732222924</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0007108075891069265</v>
+        <v>0.003515384824714957</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00179056294677058</v>
+        <v>0.002999801699699228</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.001224527762580124</v>
+        <v>-0.0004252575880155372</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.001156335673716302</v>
+        <v>0.003181322199722275</v>
       </c>
       <c r="H7" t="n">
-        <v>6.719353513182644e-05</v>
+        <v>-7.603879113556315e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>6.753365254117406e-05</v>
+        <v>4.804612427929955e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0003688632009659021</v>
+        <v>0.0001037493797114929</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01475467543964435</v>
+        <v>0.009984682898267282</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00613450415092609</v>
+        <v>0.02118142893216915</v>
       </c>
       <c r="M7" t="n">
-        <v>0.000586239564390334</v>
+        <v>-0.001155202211738149</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001670447490251042</v>
+        <v>0.002972742456542732</v>
       </c>
       <c r="O7" t="n">
-        <v>0.002412387736222638</v>
+        <v>0.002316214654547061</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01171513502232805</v>
+        <v>0.007893920368285668</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.005104377622644951</v>
+        <v>0.005496787911363488</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001103856204765374</v>
+        <v>-0.0007266795040134777</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001236910282727333</v>
+        <v>0.003112390750489813</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0006634714875707659</v>
+        <v>0.001601040613486676</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0003602536902099052</v>
+        <v>0.004404394589084809</v>
       </c>
       <c r="V7" t="n">
-        <v>8.194459221317341e-05</v>
+        <v>-3.524513735322921e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>0.006737419079128321</v>
+        <v>0.007543215555004107</v>
       </c>
       <c r="X7" t="n">
-        <v>0.00196536542335009</v>
+        <v>-0.003944979982840058</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0005092633012997227</v>
+        <v>0.0006205257824145827</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.001047214957838327</v>
+        <v>-0.0002291318087370098</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.000228501382144275</v>
+        <v>0.002078660668212301</v>
       </c>
       <c r="AB7" t="n">
-        <v>-1.920806697586208e-07</v>
+        <v>-0.0004087789656277097</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.00117454159243362</v>
+        <v>-0.001429334957675971</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.001066071224775522</v>
+        <v>-0.003659710647254893</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.001796611653269925</v>
+        <v>-0.003827841164270607</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.003721536685500854</v>
+        <v>-0.005625883913901203</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.000398074949194177</v>
+        <v>0.0001121076233184026</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.0001605379089371806</v>
+        <v>0.0002545079490997137</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.00114111830577755</v>
+        <v>-0.00196678863353667</v>
       </c>
       <c r="AK7" t="n">
-        <v>-0.001383008631799881</v>
+        <v>-0.0008992145188997768</v>
       </c>
       <c r="AL7" t="n">
-        <v>-9.586573731162895e-05</v>
+        <v>-0.000529948339094477</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.000165721928931678</v>
+        <v>0.0001281796258899181</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.002573631822368883</v>
+        <v>-0.0006542148153268201</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.0006841875463014292</v>
+        <v>-0.002225920221775602</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.0005026197622706064</v>
+        <v>0.0008157235051352796</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.001025810192230109</v>
+        <v>0.001808365905284221</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.0004948812556712701</v>
+        <v>-0.002642054675601841</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.00123433452729369</v>
+        <v>-0.001206518965843523</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0.002084650656994813</v>
+        <v>-0.006596163195652972</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.657353285362876e-05</v>
+        <v>0.002896896158103046</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.004701605168464257</v>
+        <v>0.002974011029629214</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.001551810297699174</v>
+        <v>0.000593797136423524</v>
       </c>
       <c r="AX7" t="n">
-        <v>3.421142661644283e-05</v>
+        <v>0.0003192880569547974</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.0001610411849549354</v>
+        <v>0.0006931574635045401</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-0.003607013386429931</v>
+        <v>-0.001504736429604897</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0.004615151090587566</v>
+        <v>-0.005794754900426169</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0.002343911284070665</v>
+        <v>-0.00490946614344</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.0001095246705080766</v>
+        <v>-4.820051413877979e-05</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.0001281796258899181</v>
+        <v>0.0005235718003556266</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0.0002265283087261982</v>
+        <v>-6.733251468452606e-05</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.005908734558808438</v>
+        <v>-0.003129757786426469</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.76731095037396e-05</v>
+        <v>0.0002570179454538691</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>-8.020144122179995e-05</v>
+        <v>-0.0003702744261720015</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.001730475368970547</v>
+        <v>0.001482559189193944</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.004820436809672817</v>
+        <v>-0.002889202432204274</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.0002438864860192791</v>
+        <v>0.0005345814787907244</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0.0008073928085994054</v>
+        <v>0.001361355513266571</v>
       </c>
       <c r="BN7" t="n">
-        <v>-0.0008331392543785398</v>
+        <v>-0.007565243271699685</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.0009070137369506959</v>
+        <v>-0.0004496763051320407</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.002869088702106432</v>
+        <v>0.003443617055517517</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.0001106164338621762</v>
+        <v>-0.0001595945306887614</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.001365954960733851</v>
+        <v>-0.002195940644287226</v>
       </c>
       <c r="BS7" t="n">
-        <v>-0.0003559062785570167</v>
+        <v>-0.0006890460100078045</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.0003151277161903998</v>
+        <v>-0.0003373829408706897</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.002822540691671838</v>
+        <v>0.003518774687549564</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.0001245416121895992</v>
+        <v>0.0001685367525181058</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.001934880440298425</v>
+        <v>-0.001556295763835663</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.0001309324621354635</v>
+        <v>-0.0001176622426337814</v>
       </c>
       <c r="BY7" t="n">
-        <v>-9.536215301566564e-05</v>
+        <v>-0.0002247055658769148</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0.0003547286900794366</v>
+        <v>3.629260262777423e-06</v>
       </c>
       <c r="CA7" t="n">
         <v>0</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.0002562459961562846</v>
+        <v>-0.0003527417010297018</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.0013192806965583</v>
+        <v>0.0006657987802912602</v>
       </c>
       <c r="CD7" t="n">
         <v>0</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.0002410180642698545</v>
+        <v>0.0005045389818794988</v>
       </c>
       <c r="CF7" t="n">
-        <v>-0.0004380396665119579</v>
+        <v>-0.0009943727918154898</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.0006724053096303972</v>
+        <v>0.002314481609538043</v>
       </c>
       <c r="CH7" t="n">
-        <v>-4.848797483376632e-05</v>
+        <v>-0.0001740339571837835</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.00127537457685013</v>
+        <v>-0.0004449644032554934</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.0004997419889382126</v>
+        <v>0.0003376094521177375</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.0003876400098798582</v>
+        <v>6.344983609472e-05</v>
       </c>
     </row>
     <row r="8">
@@ -2503,268 +2503,268 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002157756724265455</v>
+        <v>0.003343494814651543</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.006300218633990659</v>
+        <v>0.006125620202226237</v>
       </c>
       <c r="E8" t="n">
-        <v>0.004170077396117802</v>
+        <v>0.005713059956552727</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001461229914648826</v>
+        <v>0.003178983673249258</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001706619157518669</v>
+        <v>0.005886246699997755</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002598965525704128</v>
+        <v>0.003796170295180276</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0002419167475673667</v>
+        <v>0.0001603235993313468</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001126404850504978</v>
+        <v>0.002744742590656962</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03061697563225984</v>
+        <v>0.0225456725832783</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03029629601942579</v>
+        <v>0.02645917833524076</v>
       </c>
       <c r="M8" t="n">
-        <v>0.002580766797453893</v>
+        <v>0.001958654717058863</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0026373829911079</v>
+        <v>0.004343864709748924</v>
       </c>
       <c r="O8" t="n">
-        <v>0.005788030937258138</v>
+        <v>0.008752821579222442</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01921702939720173</v>
+        <v>0.02229437924528616</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.007455234693105111</v>
+        <v>0.009388661040266028</v>
       </c>
       <c r="R8" t="n">
-        <v>0.003394529652994369</v>
+        <v>0.0006322504996266798</v>
       </c>
       <c r="S8" t="n">
-        <v>0.004555013917781151</v>
+        <v>0.0061967684709137</v>
       </c>
       <c r="T8" t="n">
-        <v>0.001939629379634575</v>
+        <v>0.002530966316041283</v>
       </c>
       <c r="U8" t="n">
-        <v>0.004981147481964937</v>
+        <v>0.006337336481134864</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0001843851197557478</v>
+        <v>0.0001589110897175255</v>
       </c>
       <c r="W8" t="n">
-        <v>0.009105056499127712</v>
+        <v>0.01488189341541287</v>
       </c>
       <c r="X8" t="n">
-        <v>0.005147383718298124</v>
+        <v>0.0009962518670594916</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.002071952154908924</v>
+        <v>0.001163028803013699</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.001785909331897709</v>
+        <v>0.0004024804000939463</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.002240606175957352</v>
+        <v>0.002477653675864477</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.823744250754663e-05</v>
+        <v>0.0003781264561191294</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.001269676310428536</v>
+        <v>0.001335112038717184</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.003621483240053186</v>
+        <v>-0.0004584584318622742</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.002335974637733198</v>
+        <v>0.000109019119030776</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.003346412673900123</v>
+        <v>-0.0008908537780761088</v>
       </c>
       <c r="AG8" t="n">
-        <v>-4.968163210204712e-05</v>
+        <v>0.0005424214523615745</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0002426306046778709</v>
+        <v>0.0007274152448781074</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.002278281399796245</v>
+        <v>-0.0002157729569786465</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.002232158904957399</v>
+        <v>0.001197117275337681</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.0002471951043904852</v>
+        <v>0.0002792201026094038</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.0005786857730349981</v>
+        <v>0.0004483609843353248</v>
       </c>
       <c r="AN8" t="n">
-        <v>3.930498472747013e-05</v>
+        <v>0.001522347024110535</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.001956019221782943</v>
+        <v>0.001330082787803077</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0004138962165753463</v>
+        <v>0.001319880040043106</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.00210707677828299</v>
+        <v>0.003960135275376798</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.002311729932815254</v>
+        <v>0.002134496364569888</v>
       </c>
       <c r="AS8" t="n">
-        <v>-0.0004527102070128991</v>
+        <v>0.0003375579888312247</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.001016853537420137</v>
+        <v>-0.004280401993042506</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.007438234340421637</v>
+        <v>0.005166996935130524</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.006733471544864783</v>
+        <v>0.003353470630632613</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.003993858089964658</v>
+        <v>0.001772288871857466</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.0004900643830375833</v>
+        <v>0.0003937382403760431</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.0004266530588641515</v>
+        <v>0.003171553855313275</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-0.00262127913061935</v>
+        <v>0.004004457397004535</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0.000821689392736924</v>
+        <v>-0.002318217340935275</v>
       </c>
       <c r="BB8" t="n">
-        <v>-0.000719060599085447</v>
+        <v>-0.003661863542252758</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.0008157137025955829</v>
+        <v>0.000466108792592268</v>
       </c>
       <c r="BD8" t="n">
-        <v>-7.759155803846451e-06</v>
+        <v>0.0007922445093480918</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.0001035140046373978</v>
+        <v>9.668063164680607e-05</v>
       </c>
       <c r="BF8" t="n">
-        <v>-0.0002461700551833646</v>
+        <v>0.0004696047842392775</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.002703441024729333</v>
+        <v>0.00539773198926195</v>
       </c>
       <c r="BH8" t="n">
         <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.0005471174114859729</v>
+        <v>0.0001398563093015559</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.003829084661635113</v>
+        <v>0.00297184067728703</v>
       </c>
       <c r="BK8" t="n">
-        <v>-0.0003321007362069667</v>
+        <v>-0.001491596288534383</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.0006962100548416838</v>
+        <v>0.001513388399108737</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.00143220368702266</v>
+        <v>0.003283954637463343</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.0004193213550512192</v>
+        <v>-0.0004903355206130306</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.004841623202391388</v>
+        <v>0.003243288446868497</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.004957561577650657</v>
+        <v>0.004738863829238185</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.0001536895918137604</v>
+        <v>0.0001573732580765874</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.006780729064675656</v>
+        <v>0.002547384002697159</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.001908331527875562</v>
+        <v>0.00100765554167398</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.0004884689301729334</v>
+        <v>0.0004219767923202916</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.01132956339864926</v>
+        <v>0.009182546548898997</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.002518092073559216</v>
+        <v>0.002317330079238802</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.004106657918724754</v>
+        <v>0.004057854409127381</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.0002043897086261848</v>
+        <v>9.643201542914037e-05</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.000311841060607207</v>
+        <v>0.0002249250249916762</v>
       </c>
       <c r="BZ8" t="n">
-        <v>7.966715851458195e-05</v>
+        <v>0.0004879592110526521</v>
       </c>
       <c r="CA8" t="n">
         <v>0</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.0006550602461547567</v>
+        <v>0.0004524686534505495</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.00456056355430221</v>
+        <v>0.005422092383229892</v>
       </c>
       <c r="CD8" t="n">
-        <v>0</v>
+        <v>2.387014640356511e-05</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.0004760617637136367</v>
+        <v>0.000688797448947609</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.000187042528950257</v>
+        <v>3.20647193251894e-05</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.003514586097969274</v>
+        <v>0.007222899356115095</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.0007473093856363245</v>
+        <v>0.0005668767786929319</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.003823066376287357</v>
+        <v>0.0004552318325010157</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.002603460578487446</v>
+        <v>0.002594033566763176</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.001544857647549655</v>
+        <v>0.001279487630739223</v>
       </c>
     </row>
     <row r="9">
@@ -2774,268 +2774,268 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01175528507367067</v>
+        <v>0.01542819060313234</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01076824172291867</v>
+        <v>0.007655349135169754</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005124919923126148</v>
+        <v>0.01508217853689979</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001831619537275109</v>
+        <v>0.01348460291734195</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01181934657270978</v>
+        <v>0.01370916079436258</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01527866752081997</v>
+        <v>0.006621665059466464</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001057014734144723</v>
+        <v>0.0009330223258913861</v>
       </c>
       <c r="J9" t="n">
-        <v>0.005012853470437051</v>
+        <v>0.006114214773432691</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0320226591136288</v>
+        <v>0.0240919693435522</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0493593850096092</v>
+        <v>0.03350416399743755</v>
       </c>
       <c r="M9" t="n">
-        <v>0.003416048984853315</v>
+        <v>0.007734450531743498</v>
       </c>
       <c r="N9" t="n">
-        <v>0.004996796925048019</v>
+        <v>0.01299566811062983</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01659684176603282</v>
+        <v>0.0257247584138621</v>
       </c>
       <c r="P9" t="n">
-        <v>0.03434118395926161</v>
+        <v>0.04294975688816852</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.02882390745501291</v>
+        <v>0.02214010282776352</v>
       </c>
       <c r="R9" t="n">
-        <v>0.005989750160153717</v>
+        <v>0.003471552555448454</v>
       </c>
       <c r="S9" t="n">
-        <v>0.010762331838565</v>
+        <v>0.0111629456847718</v>
       </c>
       <c r="T9" t="n">
-        <v>0.005760661998726935</v>
+        <v>0.006064645118293954</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01370916079436255</v>
+        <v>0.01492835721426193</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0004163997437539702</v>
+        <v>0.0002864417568427813</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01739269698910951</v>
+        <v>0.01928640308582452</v>
       </c>
       <c r="X9" t="n">
-        <v>0.009064702114029433</v>
+        <v>0.007001620745542924</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.00512407347728</v>
+        <v>0.006428801028608211</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.003299167200512465</v>
+        <v>0.00262652146060216</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.006694426649583573</v>
+        <v>0.005575249758298461</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0003763256927813319</v>
+        <v>0.002009724473257679</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.0134208840486867</v>
+        <v>0.006460945033751242</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.01008968609865468</v>
+        <v>0.008969584109248951</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.01710442024343366</v>
+        <v>0.005704157267160825</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.005575249758298362</v>
+        <v>0.007914338919925535</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0006428801028607878</v>
+        <v>0.0008379888268156832</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.0008968609865470656</v>
+        <v>0.001166277907364233</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.004934823091247676</v>
+        <v>0.003972687771570493</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.00371556694426648</v>
+        <v>0.01012995668110634</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.004376012965964316</v>
+        <v>0.001675797615211094</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.001523500810372724</v>
+        <v>0.0009345794392523587</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.006117873158231879</v>
+        <v>0.003747597693786042</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.003435980551053452</v>
+        <v>0.002332555814728465</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.001128977078344118</v>
+        <v>0.002065978007330926</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.003363228699551524</v>
+        <v>0.01079640119960018</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.008492706645056691</v>
+        <v>0.01374392220421391</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.001102106969205807</v>
+        <v>0.004960656859390978</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.008752327746741163</v>
+        <v>0.005183116076970873</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.01205285207863354</v>
+        <v>0.0240090235256204</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.007287033869312287</v>
+        <v>0.005831389536821085</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.008616271620755889</v>
+        <v>0.009789303079416523</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.0007687379884688706</v>
+        <v>0.0008997000999666938</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.005713308244953763</v>
+        <v>0.004996817313812907</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.001814131126670926</v>
+        <v>0.01151458721291126</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.000310366232153958</v>
+        <v>0.002320335159523068</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.00400384368994231</v>
+        <v>0.002786675208199862</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.002463533225283621</v>
+        <v>0.001128977078344096</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.0005473828258638069</v>
+        <v>0.001575056252009055</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.0006107360977177789</v>
+        <v>0.0001620745542949553</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.002172563625077595</v>
+        <v>0.01160167579761524</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.005346912794398484</v>
+        <v>0.01145251396648047</v>
       </c>
       <c r="BH9" t="n">
-        <v>0</v>
+        <v>3.421142661648169e-05</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.001265822784810089</v>
+        <v>0.002513966480446972</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.006839546191247947</v>
+        <v>0.006181934657270971</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.004624456859093728</v>
+        <v>0.01139044072004968</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.001004862236628812</v>
+        <v>0.00215364834458377</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.003729045501197348</v>
+        <v>0.01197950032030748</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.003732089303565467</v>
+        <v>0.00855221012171683</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.006047103755569705</v>
+        <v>0.006831056314561823</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.007324643078833027</v>
+        <v>0.008472998137802645</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.0007687379884689039</v>
+        <v>0.0002255881405092142</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.007875281260044975</v>
+        <v>0.008687196110210672</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.002017380509000632</v>
+        <v>0.007521697203471622</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.002764384442301493</v>
+        <v>0.003032322559147005</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.01688020499679691</v>
+        <v>0.01800128122998078</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.0073670723894939</v>
+        <v>0.01115072933549431</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.01245996156310055</v>
+        <v>0.02315823190262649</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.0004177377892031431</v>
+        <v>0.0006406149903907865</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.002274183215887226</v>
+        <v>0.002528363047001581</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.0009929532351056647</v>
+        <v>0.001024208566108054</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>6.445375443120405e-05</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.002852512155591536</v>
+        <v>0.002296710117939216</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.01281812538795779</v>
+        <v>0.008690254500310413</v>
       </c>
       <c r="CD9" t="n">
         <v>9.310986964619072e-05</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.001121076233183826</v>
+        <v>0.001532822392535849</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.00074554294975685</v>
+        <v>0.002917341977309551</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.009692058346839528</v>
+        <v>0.01128038897893029</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.002203600248293003</v>
+        <v>0.002358783364369987</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.004866258459555228</v>
+        <v>0.004314090626939815</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.01310057655349132</v>
+        <v>0.004181523500810358</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.002062520141798208</v>
+        <v>0.008572349339349051</v>
       </c>
     </row>
   </sheetData>
